--- a/Morosos/informe_reporte_morosos.xlsx
+++ b/Morosos/informe_reporte_morosos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\dev\process_python_cpcs\Morosos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29AA808B-61FE-4FF3-8894-398B225EA77A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A440EA-AB1F-4A37-81E1-931753D4C056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="183">
   <si>
     <t>identificacion</t>
   </si>
@@ -49,262 +49,526 @@
     <t>deuda total</t>
   </si>
   <si>
-    <t>1025904113</t>
-  </si>
-  <si>
-    <t>1033198814</t>
-  </si>
-  <si>
-    <t>1141352259</t>
-  </si>
-  <si>
-    <t>1018254177</t>
-  </si>
-  <si>
-    <t>1054882046</t>
-  </si>
-  <si>
-    <t>1192469448</t>
-  </si>
-  <si>
-    <t>1011518603</t>
-  </si>
-  <si>
-    <t>1155716876</t>
+    <t>1013464926</t>
+  </si>
+  <si>
+    <t>1013466654</t>
+  </si>
+  <si>
+    <t>1011514095</t>
+  </si>
+  <si>
+    <t>1021935485</t>
+  </si>
+  <si>
+    <t>1025898446</t>
+  </si>
+  <si>
+    <t>1025895387</t>
+  </si>
+  <si>
+    <t>1035003747</t>
+  </si>
+  <si>
+    <t>1202213225</t>
+  </si>
+  <si>
+    <t>1013353521</t>
+  </si>
+  <si>
+    <t>1013362371</t>
+  </si>
+  <si>
+    <t>1025902964</t>
+  </si>
+  <si>
+    <t>1041634370</t>
+  </si>
+  <si>
+    <t>1021931357</t>
+  </si>
+  <si>
+    <t>1020308169</t>
+  </si>
+  <si>
+    <t>1020228828</t>
+  </si>
+  <si>
+    <t>1025899613</t>
+  </si>
+  <si>
+    <t>1035005666</t>
+  </si>
+  <si>
+    <t>1018253841</t>
+  </si>
+  <si>
+    <t>1020307672</t>
+  </si>
+  <si>
+    <t>1011519079</t>
+  </si>
+  <si>
+    <t>1011516886</t>
+  </si>
+  <si>
+    <t>1027664379</t>
+  </si>
+  <si>
+    <t>1027663704</t>
+  </si>
+  <si>
+    <t>1020312315</t>
+  </si>
+  <si>
+    <t>1021941636</t>
   </si>
   <si>
     <t>1013368945</t>
   </si>
   <si>
-    <t>1015075125</t>
+    <t>1035008500</t>
   </si>
   <si>
     <t>1025904957</t>
   </si>
   <si>
-    <t>1037676515</t>
-  </si>
-  <si>
     <t>1018271176</t>
   </si>
   <si>
     <t>1018254757</t>
   </si>
   <si>
-    <t>1084474489</t>
+    <t>1141722491</t>
+  </si>
+  <si>
+    <t>1141719278</t>
+  </si>
+  <si>
+    <t>1069762747</t>
+  </si>
+  <si>
+    <t>1069756765</t>
+  </si>
+  <si>
+    <t>1011106856</t>
   </si>
   <si>
     <t>1025667898</t>
   </si>
   <si>
-    <t>1023655274</t>
-  </si>
-  <si>
-    <t>Agudelo Luciana</t>
-  </si>
-  <si>
-    <t>Carmona Taborda Luciana</t>
-  </si>
-  <si>
-    <t>Fonseca Rivera Emily Sofia</t>
-  </si>
-  <si>
-    <t>Garcia Correa Andres Esteban</t>
-  </si>
-  <si>
-    <t>Gomez Leon Mateo</t>
-  </si>
-  <si>
-    <t>Marquez Mora Emilia</t>
-  </si>
-  <si>
-    <t>Ospina Cifuentes Antonella</t>
-  </si>
-  <si>
-    <t>Quintero Suarez Andres David</t>
+    <t>1025901666</t>
+  </si>
+  <si>
+    <t>1034925183</t>
+  </si>
+  <si>
+    <t>1025900606</t>
+  </si>
+  <si>
+    <t>Cardona Mosquera Isaac</t>
+  </si>
+  <si>
+    <t>Cardona Mosquera Roxana</t>
+  </si>
+  <si>
+    <t>Castaño Viloria Sara</t>
+  </si>
+  <si>
+    <t>Clavijo Quiceno Sara</t>
+  </si>
+  <si>
+    <t>Cortes Correa Rebeca</t>
+  </si>
+  <si>
+    <t>Cortes Correa Salome</t>
+  </si>
+  <si>
+    <t>Cuervo Consuegra Tamara</t>
+  </si>
+  <si>
+    <t>De Luquez Bernal Mabel Sarai</t>
+  </si>
+  <si>
+    <t>Garcia Ramirez Nicolas</t>
+  </si>
+  <si>
+    <t>Garcia Ramirez Thomás</t>
+  </si>
+  <si>
+    <t>Hurtado Hurtado Sara</t>
+  </si>
+  <si>
+    <t>Jaramillo Agudelo Ana Sofia</t>
+  </si>
+  <si>
+    <t>Machado Taborda Mateo</t>
+  </si>
+  <si>
+    <t>Manco Fonnegra Samuel</t>
+  </si>
+  <si>
+    <t>Mariaca Montagut Maria Clara</t>
+  </si>
+  <si>
+    <t>Martinez Alvarez Thiago</t>
+  </si>
+  <si>
+    <t>Martinez Ciro Josue</t>
+  </si>
+  <si>
+    <t>Mendoza Alvarez Abigail</t>
+  </si>
+  <si>
+    <t>Muñoz Vellojin Mateo</t>
+  </si>
+  <si>
+    <t>Orrego Jimenez Analucia</t>
+  </si>
+  <si>
+    <t>Orrego Jimenez Benjamin</t>
+  </si>
+  <si>
+    <t>Prieto Albán Isaac</t>
+  </si>
+  <si>
+    <t>Prieto Albán Mathías</t>
+  </si>
+  <si>
+    <t>Pérez Hernández Salomé</t>
+  </si>
+  <si>
+    <t>Rojas Jimenez Sofia</t>
   </si>
   <si>
     <t>Ruiz Estrada Sofia Camila</t>
   </si>
   <si>
-    <t>Ruiz Rodas Jacobo</t>
+    <t>Sanabria Cardona Santiago</t>
   </si>
   <si>
     <t>Sanchez Justiniano Jose David</t>
   </si>
   <si>
-    <t>Santos Paz Ezra Wolf</t>
-  </si>
-  <si>
     <t>Sayago Acevedo Isabella</t>
   </si>
   <si>
     <t>Sayago Acevedo Samuel</t>
   </si>
   <si>
-    <t>Tenorio Maya Liam</t>
+    <t>Segura Rios Emmanuel David</t>
+  </si>
+  <si>
+    <t>Segura Rios Samuel Felipe</t>
+  </si>
+  <si>
+    <t>Sorza Hernandez Juan Martin</t>
+  </si>
+  <si>
+    <t>Sorza Hernandez Maria Juliana</t>
+  </si>
+  <si>
+    <t>Suarez Bayona Martina</t>
   </si>
   <si>
     <t>Troya Rendon Emanuel</t>
   </si>
   <si>
-    <t>Zambrano Mejia Mariangel</t>
+    <t>Vanegas Olaya Simon</t>
+  </si>
+  <si>
+    <t>Vanegas Pulgarin Sheray</t>
+  </si>
+  <si>
+    <t>Velez Ortiz Simon</t>
+  </si>
+  <si>
+    <t>SEXTO</t>
   </si>
   <si>
     <t>SEGUNDO</t>
   </si>
   <si>
+    <t>ONCE</t>
+  </si>
+  <si>
+    <t>OCTAVO</t>
+  </si>
+  <si>
+    <t>SEPTIMO</t>
+  </si>
+  <si>
+    <t>DÉCIMO</t>
+  </si>
+  <si>
+    <t>TERCERO</t>
+  </si>
+  <si>
+    <t>QUINTO</t>
+  </si>
+  <si>
+    <t>NOVENO</t>
+  </si>
+  <si>
     <t>CUARTO</t>
   </si>
   <si>
-    <t>SEPTIMO</t>
-  </si>
-  <si>
-    <t>SEXTO</t>
-  </si>
-  <si>
-    <t>PRIMERO</t>
-  </si>
-  <si>
-    <t>TERCERO</t>
-  </si>
-  <si>
-    <t>DÉCIMO</t>
-  </si>
-  <si>
-    <t>Agudelo Juliet Cristina</t>
-  </si>
-  <si>
-    <t>Correa Claudia Patricia</t>
-  </si>
-  <si>
-    <t>David Mercado Andres Felipe</t>
-  </si>
-  <si>
-    <t>Correa Osorio Luisa Fernanda</t>
-  </si>
-  <si>
-    <t>Gomez Serna Daniel</t>
-  </si>
-  <si>
-    <t>Mora Cardona Katherine</t>
-  </si>
-  <si>
-    <t>Ospina Escobar Nilson James</t>
-  </si>
-  <si>
-    <t>Quintero Gerardino Jairo Andres</t>
+    <t>Mosquera Rodriguez Tania Karina</t>
+  </si>
+  <si>
+    <t>Viloria Montoya Isabel Cristina</t>
+  </si>
+  <si>
+    <t>Carreño Bohorquez Nora Maria</t>
+  </si>
+  <si>
+    <t>Cortes Velasquez Juan Pablo</t>
+  </si>
+  <si>
+    <t>Cuervo Paternina Eder Andres</t>
+  </si>
+  <si>
+    <t>De Luquez Diaz Ezequiel</t>
+  </si>
+  <si>
+    <t>Ramirez Suarez Leidy Tatiana</t>
+  </si>
+  <si>
+    <t>Garcia Valencia Cesar Augusto</t>
+  </si>
+  <si>
+    <t>Hurtado Orozco Yudi Andrea</t>
+  </si>
+  <si>
+    <t>Agudelo Torres Sumilde Elena</t>
+  </si>
+  <si>
+    <t>Sas Inversiones Myt</t>
+  </si>
+  <si>
+    <t>Manco Echavarria Reynel De Jesus</t>
+  </si>
+  <si>
+    <t>Montagut Ortiz Clariveth</t>
+  </si>
+  <si>
+    <t>Hernandez Morelo Liliana</t>
+  </si>
+  <si>
+    <t>Martinez Moreno Devinson</t>
+  </si>
+  <si>
+    <t>Alvarez Martinez Glenys Yanet</t>
+  </si>
+  <si>
+    <t>Vellojin Cavadia Tania Marjolia</t>
+  </si>
+  <si>
+    <t>Orrego Zuluaga Juan Esteban</t>
+  </si>
+  <si>
+    <t>Prieto Oyaga Cristhian Camilo</t>
+  </si>
+  <si>
+    <t>Hernandez Cardona Mauricio</t>
+  </si>
+  <si>
+    <t>Marino Millan Yelitza Rossana</t>
   </si>
   <si>
     <t>Estrada Colon Yerica Del Carmen</t>
   </si>
   <si>
-    <t>Rodas Marin Monica Janeth</t>
+    <t>Sanabria Ballen Andres Leonardo</t>
   </si>
   <si>
     <t>Sanchez Justiniano Martha Catherine</t>
   </si>
   <si>
-    <t>Santos Lopez Sebastian</t>
-  </si>
-  <si>
     <t>Sayago Montes Juan Esteban</t>
   </si>
   <si>
     <t>Acevedo Galeano Viviana</t>
   </si>
   <si>
-    <t>Marin Osorio Johny Alexander</t>
+    <t>Segura Camacho Oscar Dario</t>
+  </si>
+  <si>
+    <t>Hernandez Baron Lina Paola</t>
+  </si>
+  <si>
+    <t>Bayona Buitrago Sandra Milena</t>
   </si>
   <si>
     <t>Troya Osorio Manuel Enrique</t>
   </si>
   <si>
-    <t>Santana Marulanda Stuart</t>
+    <t>Olaya Rojas Liliana Maria</t>
+  </si>
+  <si>
+    <t>Vanegas Zuñiga Ray Andres</t>
+  </si>
+  <si>
+    <t>Ortiz Velez Laura Catalina</t>
+  </si>
+  <si>
+    <t>Padre</t>
   </si>
   <si>
     <t>Madre</t>
   </si>
   <si>
-    <t>Padre</t>
-  </si>
-  <si>
-    <t>Padrastro</t>
-  </si>
-  <si>
-    <t>3102032602</t>
-  </si>
-  <si>
-    <t>3148691862</t>
+    <t>5095498</t>
+  </si>
+  <si>
+    <t>5467166</t>
+  </si>
+  <si>
+    <t>4432431</t>
+  </si>
+  <si>
+    <t>2973675</t>
+  </si>
+  <si>
+    <t>2068714</t>
+  </si>
+  <si>
+    <t>5823889</t>
+  </si>
+  <si>
+    <t>4076883</t>
+  </si>
+  <si>
+    <t>5038065</t>
+  </si>
+  <si>
+    <t>4195996</t>
+  </si>
+  <si>
+    <t>3136549427</t>
+  </si>
+  <si>
+    <t>4224748</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>3013564721</t>
-  </si>
-  <si>
-    <t>3013620164</t>
-  </si>
-  <si>
-    <t>3233605163</t>
-  </si>
-  <si>
-    <t>2840252</t>
-  </si>
-  <si>
-    <t>3117634856</t>
-  </si>
-  <si>
-    <t>3205617348</t>
-  </si>
-  <si>
-    <t>agudeloluciana90@gmail.com</t>
-  </si>
-  <si>
-    <t>geraldinetabordacardona@gmail.com</t>
-  </si>
-  <si>
-    <t>leidypaorivera@gmail.com</t>
-  </si>
-  <si>
-    <t>fercorreaosorio25@gmail.com</t>
-  </si>
-  <si>
-    <t>yeimyleon8904@gmail.com</t>
-  </si>
-  <si>
-    <t>ktmc-10@hotmail.com</t>
-  </si>
-  <si>
-    <t>y-ulivale@hotmail.com</t>
-  </si>
-  <si>
-    <t>yohelissuarez@gmail.com</t>
+    <t>2050489</t>
+  </si>
+  <si>
+    <t>5700932</t>
+  </si>
+  <si>
+    <t>3006234263</t>
+  </si>
+  <si>
+    <t>3178333446</t>
+  </si>
+  <si>
+    <t>3022703240</t>
+  </si>
+  <si>
+    <t>2347767</t>
+  </si>
+  <si>
+    <t>5863905</t>
+  </si>
+  <si>
+    <t>4886484</t>
+  </si>
+  <si>
+    <t>4882576</t>
+  </si>
+  <si>
+    <t>ANDRESCARDONA70@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>CLAUDIAYAVIMO@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>marybella2905@gmail.com</t>
+  </si>
+  <si>
+    <t>ALEJANDRA210187@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>mercadeo@vertigologistica.com</t>
+  </si>
+  <si>
+    <t>marlencj@hotmail.com</t>
+  </si>
+  <si>
+    <t>EZDEDI7@YAHOO.ES</t>
+  </si>
+  <si>
+    <t>Ramirezsuarezt@gmail.com</t>
+  </si>
+  <si>
+    <t>SEAGUDELOT@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>SELVAAZUL_07@YAHOO.ES</t>
+  </si>
+  <si>
+    <t>REYNELM1980@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>alejomtoro1@gmail.com</t>
+  </si>
+  <si>
+    <t>EZEQUIELMARTINEZ-5@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>alexandraa200906@gmail.com</t>
+  </si>
+  <si>
+    <t>glenysyanett@hotmail.com</t>
+  </si>
+  <si>
+    <t>TANIAVELCAV@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>NATALIAJIMENEZCOMUNICACIONES@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>luiza1415@hotmail.es</t>
+  </si>
+  <si>
+    <t>PAOLAHC0312@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>pablopoderoso@gmail.com</t>
   </si>
   <si>
     <t>estradayerica2430@gmail.com</t>
   </si>
   <si>
-    <t>MONICA.RODASM@GMAIL.COM</t>
+    <t>sanabriaandres501@Gmail.com</t>
   </si>
   <si>
     <t>marthacsanchezj@gmail.com</t>
   </si>
   <si>
-    <t>ss7canada@gmail.com</t>
-  </si>
-  <si>
     <t>VIACEGA@GMAIL.COM</t>
   </si>
   <si>
-    <t>sunandbeach88@hotmail.com</t>
+    <t>lilios12@hotmail.com</t>
+  </si>
+  <si>
+    <t>juliocesar@sorza.com</t>
+  </si>
+  <si>
+    <t>samy587@hotmail.com</t>
   </si>
   <si>
     <t>manuel.troya734@casur.gov.co</t>
   </si>
   <si>
-    <t>zantana07@gmail.com</t>
+    <t>sherayvp@gmail.com</t>
+  </si>
+  <si>
+    <t>LAURAORTIZ.PSICOLOGIA@GMAIL.COM</t>
   </si>
 </sst>
 </file>
@@ -322,6 +586,7 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -336,7 +601,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -678,17 +943,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="34" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -726,28 +991,28 @@
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="G2" s="1">
-        <v>3137650642</v>
+        <v>3185029620</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>79</v>
+        <v>153</v>
       </c>
       <c r="I2" s="1">
-        <v>5470470</v>
+        <v>1242434</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -755,28 +1020,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>71</v>
+        <v>132</v>
       </c>
       <c r="G3" s="1">
-        <v>3006153207</v>
+        <v>3185029620</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="I3" s="1">
-        <v>3562726</v>
+        <v>1423984</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -784,28 +1049,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>72</v>
+        <v>133</v>
       </c>
       <c r="G4" s="1">
-        <v>3002731587</v>
+        <v>3148494120</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="I4" s="1">
-        <v>804948</v>
+        <v>970720</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -813,28 +1078,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>67</v>
+        <v>131</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="G5" s="1">
-        <v>3013564721</v>
+        <v>3016959292</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="I5" s="1">
-        <v>2512680</v>
+        <v>1242434</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -842,28 +1107,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>67</v>
+        <v>131</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>72</v>
+        <v>135</v>
       </c>
       <c r="G6" s="1">
-        <v>3160524609</v>
+        <v>3012457263</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>83</v>
+        <v>156</v>
       </c>
       <c r="I6" s="1">
-        <v>2262772</v>
+        <v>1007440</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -871,28 +1136,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>72</v>
+        <v>135</v>
       </c>
       <c r="G7" s="1">
-        <v>3116823407</v>
+        <v>3012457266</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>84</v>
+        <v>157</v>
       </c>
       <c r="I7" s="1">
-        <v>1472088</v>
+        <v>913296</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -900,28 +1165,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="G8" s="1">
-        <v>3013620164</v>
+        <v>3233179080</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>85</v>
+        <v>158</v>
       </c>
       <c r="I8" s="1">
-        <v>3024840</v>
+        <v>1265122</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -929,28 +1194,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="G9" s="1">
-        <v>3233605163</v>
+        <v>3156803375</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>86</v>
+        <v>159</v>
       </c>
       <c r="I9" s="1">
-        <v>2709144</v>
+        <v>1136976</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -958,28 +1223,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>58</v>
+        <v>103</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>67</v>
+        <v>131</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>72</v>
+        <v>138</v>
       </c>
       <c r="G10" s="1">
-        <v>3106368274</v>
+        <v>3146320382</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>87</v>
+        <v>160</v>
       </c>
       <c r="I10" s="1">
-        <v>2078650</v>
+        <v>803508</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -987,28 +1252,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>67</v>
+        <v>131</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="G11" s="1">
-        <v>3008674834</v>
+        <v>3146320382</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="I11" s="1">
-        <v>1515860</v>
+        <v>862598</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -1016,28 +1281,20 @@
         <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G12" s="1">
-        <v>3168660548</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>89</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
       <c r="I12" s="1">
-        <v>1771470</v>
+        <v>1047586</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1045,28 +1302,28 @@
         <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>68</v>
+        <v>131</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="G13" s="1">
-        <v>3028133419</v>
+        <v>3102013484</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>90</v>
+        <v>161</v>
       </c>
       <c r="I13" s="1">
-        <v>1196214</v>
+        <v>956502</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -1074,28 +1331,28 @@
         <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>62</v>
+        <v>107</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>72</v>
+        <v>140</v>
       </c>
       <c r="G14" s="1">
-        <v>3207608861</v>
+        <v>3136146481</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>91</v>
+        <v>162</v>
       </c>
       <c r="I14" s="1">
-        <v>3542736</v>
+        <v>1141872</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -1103,28 +1360,28 @@
         <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>63</v>
+        <v>108</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>72</v>
+        <v>141</v>
       </c>
       <c r="G15" s="1">
-        <v>3207608861</v>
+        <v>3017206508</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>91</v>
+        <v>163</v>
       </c>
       <c r="I15" s="1">
-        <v>5708870</v>
+        <v>956502</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -1132,28 +1389,28 @@
         <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>64</v>
+        <v>109</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="G16" s="1">
-        <v>3205617348</v>
+        <v>3113448104</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>92</v>
+        <v>164</v>
       </c>
       <c r="I16" s="1">
-        <v>1314565</v>
+        <v>1070822</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -1161,28 +1418,28 @@
         <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>45</v>
+        <v>91</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>68</v>
+        <v>131</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>72</v>
+        <v>143</v>
       </c>
       <c r="G17" s="1">
-        <v>3206798318</v>
+        <v>3013807813</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>93</v>
+        <v>165</v>
       </c>
       <c r="I17" s="1">
-        <v>1405060</v>
+        <v>1198148</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -1190,28 +1447,658 @@
         <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G18" s="1">
+        <v>3186656220</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1172972</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G19" s="1">
+        <v>3012100135</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="I19" s="1">
+        <v>1141872</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="G20" s="1">
+        <v>3015954319</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1016660</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G21" s="1">
+        <v>3006234263</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="I21" s="1">
+        <v>1441698</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G22" s="1">
+        <v>3006234263</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="I22" s="1">
+        <v>1265122</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="G23" s="1">
+        <v>3178333446</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I23" s="1">
+        <v>1212598</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="G24" s="1">
+        <v>3178333446</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I24" s="1">
+        <v>1103508</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G25" s="1">
+        <v>3226367303</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="I25" s="1">
+        <v>1007440</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G26" s="1">
+        <v>3022703240</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I26" s="1">
+        <v>1303544</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G27" s="1">
+        <v>3106368274</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="I27" s="1">
+        <v>970720</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="G28" s="1">
+        <v>3022424243</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="I28" s="1">
+        <v>800648</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G29" s="1">
+        <v>3168660548</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="I29" s="1">
+        <v>1212598</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G30" s="1">
+        <v>3207608861</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I30" s="1">
+        <v>1423984</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G31" s="1">
+        <v>3207608861</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I31" s="1">
+        <v>1134204</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G32" s="1">
+        <v>3148214908</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="I32" s="1">
+        <v>1172972</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G33" s="1">
+        <v>3148214908</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="I33" s="1">
+        <v>1016660</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G34" s="1">
+        <v>3004608087</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="I34" s="1">
+        <v>1047586</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="B35" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G35" s="1">
+        <v>3004608087</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="I35" s="1">
+        <v>1034046</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G18" s="1">
-        <v>3003183744</v>
-      </c>
-      <c r="H18" s="1" t="s">
+      <c r="B36" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G36" s="1">
+        <v>3115341734</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="I36" s="1">
+        <v>1131172</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G37" s="1">
+        <v>3206798318</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="I37" s="1">
+        <v>899987</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="I18" s="1">
-        <v>2380588</v>
+      <c r="D38" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1">
+        <v>1329096</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G39" s="1">
+        <v>3128021315</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="I39" s="1">
+        <v>1047586</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G40" s="1">
+        <v>3002799011</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="I40" s="1">
+        <v>1034046</v>
       </c>
     </row>
   </sheetData>
